--- a/ExcelData/TableProjectile.xlsx
+++ b/ExcelData/TableProjectile.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\Mole_Fork\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09C3603-00DC-41CA-B0F5-AB06A64DEC62}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{750009F0-AE51-4859-9062-ADF5F66EFC92}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21135" windowHeight="10980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21135" windowHeight="10980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Single" sheetId="1" r:id="rId1"/>
+    <sheet name="NOTE" sheetId="2" r:id="rId1"/>
+    <sheet name="Single" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -101,7 +102,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -272,58 +273,58 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1">
@@ -608,6 +609,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78D5D2EF-1765-4F88-9967-9052D7AE5B9F}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L31"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -623,66 +634,66 @@
       <c r="A1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="6" t="s">
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="13" t="s">
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="14"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="18" t="s">
+      <c r="J1" s="6"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="8" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="6" t="s">
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6" t="s">
+      <c r="F2" s="3"/>
+      <c r="G2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="11"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="19"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="13"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="2" t="s">
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="9"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="19"/>
       <c r="L3" s="20"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
